--- a/ejemplos/nuevo.xlsx
+++ b/ejemplos/nuevo.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="E2" t="n">
         <v>180</v>
